--- a/input/question_bank_72.xlsx
+++ b/input/question_bank_72.xlsx
@@ -40,1084 +40,1084 @@
     <t>difficulty</t>
   </si>
   <si>
-    <t>Hard Question 1: What is the solution to this complex problem?</t>
-  </si>
-  <si>
-    <t>Hard Question 2: What is the solution to this complex problem?</t>
-  </si>
-  <si>
-    <t>Hard Question 3: What is the solution to this complex problem?</t>
-  </si>
-  <si>
-    <t>Hard Question 4: What is the solution to this complex problem?</t>
-  </si>
-  <si>
-    <t>Hard Question 5: What is the solution to this complex problem?</t>
-  </si>
-  <si>
-    <t>Hard Question 6: What is the solution to this complex problem?</t>
-  </si>
-  <si>
-    <t>Hard Question 7: What is the solution to this complex problem?</t>
-  </si>
-  <si>
-    <t>Hard Question 8: What is the solution to this complex problem?</t>
-  </si>
-  <si>
-    <t>Hard Question 9: What is the solution to this complex problem?</t>
-  </si>
-  <si>
-    <t>Hard Question 10: What is the solution to this complex problem?</t>
-  </si>
-  <si>
-    <t>Hard Question 11: What is the solution to this complex problem?</t>
-  </si>
-  <si>
-    <t>Hard Question 12: What is the solution to this complex problem?</t>
-  </si>
-  <si>
-    <t>Medium Question 1: Calculate the following expression.</t>
-  </si>
-  <si>
-    <t>Medium Question 2: Calculate the following expression.</t>
-  </si>
-  <si>
-    <t>Medium Question 3: Calculate the following expression.</t>
-  </si>
-  <si>
-    <t>Medium Question 4: Calculate the following expression.</t>
-  </si>
-  <si>
-    <t>Medium Question 5: Calculate the following expression.</t>
-  </si>
-  <si>
-    <t>Medium Question 6: Calculate the following expression.</t>
-  </si>
-  <si>
-    <t>Medium Question 7: Calculate the following expression.</t>
-  </si>
-  <si>
-    <t>Medium Question 8: Calculate the following expression.</t>
-  </si>
-  <si>
-    <t>Medium Question 9: Calculate the following expression.</t>
-  </si>
-  <si>
-    <t>Medium Question 10: Calculate the following expression.</t>
-  </si>
-  <si>
-    <t>Medium Question 11: Calculate the following expression.</t>
-  </si>
-  <si>
-    <t>Medium Question 12: Calculate the following expression.</t>
-  </si>
-  <si>
-    <t>Medium Question 13: Calculate the following expression.</t>
-  </si>
-  <si>
-    <t>Medium Question 14: Calculate the following expression.</t>
-  </si>
-  <si>
-    <t>Medium Question 15: Calculate the following expression.</t>
-  </si>
-  <si>
-    <t>Medium Question 16: Calculate the following expression.</t>
-  </si>
-  <si>
-    <t>Medium Question 17: Calculate the following expression.</t>
-  </si>
-  <si>
-    <t>Medium Question 18: Calculate the following expression.</t>
-  </si>
-  <si>
-    <t>Medium Question 19: Calculate the following expression.</t>
-  </si>
-  <si>
-    <t>Medium Question 20: Calculate the following expression.</t>
-  </si>
-  <si>
-    <t>Medium Question 21: Calculate the following expression.</t>
-  </si>
-  <si>
-    <t>Medium Question 22: Calculate the following expression.</t>
-  </si>
-  <si>
-    <t>Medium Question 23: Calculate the following expression.</t>
-  </si>
-  <si>
-    <t>Medium Question 24: Calculate the following expression.</t>
-  </si>
-  <si>
-    <t>Medium Question 25: Calculate the following expression.</t>
-  </si>
-  <si>
-    <t>Medium Question 26: Calculate the following expression.</t>
-  </si>
-  <si>
-    <t>Medium Question 27: Calculate the following expression.</t>
-  </si>
-  <si>
-    <t>Medium Question 28: Calculate the following expression.</t>
-  </si>
-  <si>
-    <t>Medium Question 29: Calculate the following expression.</t>
-  </si>
-  <si>
-    <t>Medium Question 30: Calculate the following expression.</t>
-  </si>
-  <si>
-    <t>Easy Question 1: What is the basic definition of this term?</t>
-  </si>
-  <si>
-    <t>Easy Question 2: What is the basic definition of this term?</t>
-  </si>
-  <si>
-    <t>Easy Question 3: What is the basic definition of this term?</t>
-  </si>
-  <si>
-    <t>Easy Question 4: What is the basic definition of this term?</t>
-  </si>
-  <si>
-    <t>Easy Question 5: What is the basic definition of this term?</t>
-  </si>
-  <si>
-    <t>Easy Question 6: What is the basic definition of this term?</t>
-  </si>
-  <si>
-    <t>Easy Question 7: What is the basic definition of this term?</t>
-  </si>
-  <si>
-    <t>Easy Question 8: What is the basic definition of this term?</t>
-  </si>
-  <si>
-    <t>Easy Question 9: What is the basic definition of this term?</t>
-  </si>
-  <si>
-    <t>Easy Question 10: What is the basic definition of this term?</t>
-  </si>
-  <si>
-    <t>Easy Question 11: What is the basic definition of this term?</t>
-  </si>
-  <si>
-    <t>Easy Question 12: What is the basic definition of this term?</t>
-  </si>
-  <si>
-    <t>Easy Question 13: What is the basic definition of this term?</t>
-  </si>
-  <si>
-    <t>Easy Question 14: What is the basic definition of this term?</t>
-  </si>
-  <si>
-    <t>Easy Question 15: What is the basic definition of this term?</t>
-  </si>
-  <si>
-    <t>Easy Question 16: What is the basic definition of this term?</t>
-  </si>
-  <si>
-    <t>Easy Question 17: What is the basic definition of this term?</t>
-  </si>
-  <si>
-    <t>Easy Question 18: What is the basic definition of this term?</t>
-  </si>
-  <si>
-    <t>Easy Question 19: What is the basic definition of this term?</t>
-  </si>
-  <si>
-    <t>Easy Question 20: What is the basic definition of this term?</t>
-  </si>
-  <si>
-    <t>Easy Question 21: What is the basic definition of this term?</t>
-  </si>
-  <si>
-    <t>Easy Question 22: What is the basic definition of this term?</t>
-  </si>
-  <si>
-    <t>Easy Question 23: What is the basic definition of this term?</t>
-  </si>
-  <si>
-    <t>Easy Question 24: What is the basic definition of this term?</t>
-  </si>
-  <si>
-    <t>Easy Question 25: What is the basic definition of this term?</t>
-  </si>
-  <si>
-    <t>Easy Question 26: What is the basic definition of this term?</t>
-  </si>
-  <si>
-    <t>Easy Question 27: What is the basic definition of this term?</t>
-  </si>
-  <si>
-    <t>Easy Question 28: What is the basic definition of this term?</t>
-  </si>
-  <si>
-    <t>Easy Question 29: What is the basic definition of this term?</t>
-  </si>
-  <si>
-    <t>Easy Question 30: What is the basic definition of this term?</t>
-  </si>
-  <si>
-    <t>Hard option A1</t>
-  </si>
-  <si>
-    <t>Hard option A2</t>
-  </si>
-  <si>
-    <t>Hard option A3</t>
-  </si>
-  <si>
-    <t>Hard option A4</t>
-  </si>
-  <si>
-    <t>Hard option A5</t>
-  </si>
-  <si>
-    <t>Hard option A6</t>
-  </si>
-  <si>
-    <t>Hard option A7</t>
-  </si>
-  <si>
-    <t>Hard option A8</t>
-  </si>
-  <si>
-    <t>Hard option A9</t>
-  </si>
-  <si>
-    <t>Hard option A10</t>
-  </si>
-  <si>
-    <t>Hard option A11</t>
-  </si>
-  <si>
-    <t>Hard option A12</t>
-  </si>
-  <si>
-    <t>Medium option A1</t>
-  </si>
-  <si>
-    <t>Medium option A2</t>
-  </si>
-  <si>
-    <t>Medium option A3</t>
-  </si>
-  <si>
-    <t>Medium option A4</t>
-  </si>
-  <si>
-    <t>Medium option A5</t>
-  </si>
-  <si>
-    <t>Medium option A6</t>
-  </si>
-  <si>
-    <t>Medium option A7</t>
-  </si>
-  <si>
-    <t>Medium option A8</t>
-  </si>
-  <si>
-    <t>Medium option A9</t>
-  </si>
-  <si>
-    <t>Medium option A10</t>
-  </si>
-  <si>
-    <t>Medium option A11</t>
-  </si>
-  <si>
-    <t>Medium option A12</t>
-  </si>
-  <si>
-    <t>Medium option A13</t>
-  </si>
-  <si>
-    <t>Medium option A14</t>
-  </si>
-  <si>
-    <t>Medium option A15</t>
-  </si>
-  <si>
-    <t>Medium option A16</t>
-  </si>
-  <si>
-    <t>Medium option A17</t>
-  </si>
-  <si>
-    <t>Medium option A18</t>
-  </si>
-  <si>
-    <t>Medium option A19</t>
-  </si>
-  <si>
-    <t>Medium option A20</t>
-  </si>
-  <si>
-    <t>Medium option A21</t>
-  </si>
-  <si>
-    <t>Medium option A22</t>
-  </si>
-  <si>
-    <t>Medium option A23</t>
-  </si>
-  <si>
-    <t>Medium option A24</t>
-  </si>
-  <si>
-    <t>Medium option A25</t>
-  </si>
-  <si>
-    <t>Medium option A26</t>
-  </si>
-  <si>
-    <t>Medium option A27</t>
-  </si>
-  <si>
-    <t>Medium option A28</t>
-  </si>
-  <si>
-    <t>Medium option A29</t>
-  </si>
-  <si>
-    <t>Medium option A30</t>
-  </si>
-  <si>
-    <t>Easy option A1</t>
-  </si>
-  <si>
-    <t>Easy option A2</t>
-  </si>
-  <si>
-    <t>Easy option A3</t>
-  </si>
-  <si>
-    <t>Easy option A4</t>
-  </si>
-  <si>
-    <t>Easy option A5</t>
-  </si>
-  <si>
-    <t>Easy option A6</t>
-  </si>
-  <si>
-    <t>Easy option A7</t>
-  </si>
-  <si>
-    <t>Easy option A8</t>
-  </si>
-  <si>
-    <t>Easy option A9</t>
-  </si>
-  <si>
-    <t>Easy option A10</t>
-  </si>
-  <si>
-    <t>Easy option A11</t>
-  </si>
-  <si>
-    <t>Easy option A12</t>
-  </si>
-  <si>
-    <t>Easy option A13</t>
-  </si>
-  <si>
-    <t>Easy option A14</t>
-  </si>
-  <si>
-    <t>Easy option A15</t>
-  </si>
-  <si>
-    <t>Easy option A16</t>
-  </si>
-  <si>
-    <t>Easy option A17</t>
-  </si>
-  <si>
-    <t>Easy option A18</t>
-  </si>
-  <si>
-    <t>Easy option A19</t>
-  </si>
-  <si>
-    <t>Easy option A20</t>
-  </si>
-  <si>
-    <t>Easy option A21</t>
-  </si>
-  <si>
-    <t>Easy option A22</t>
-  </si>
-  <si>
-    <t>Easy option A23</t>
-  </si>
-  <si>
-    <t>Easy option A24</t>
-  </si>
-  <si>
-    <t>Easy option A25</t>
-  </si>
-  <si>
-    <t>Easy option A26</t>
-  </si>
-  <si>
-    <t>Easy option A27</t>
-  </si>
-  <si>
-    <t>Easy option A28</t>
-  </si>
-  <si>
-    <t>Easy option A29</t>
-  </si>
-  <si>
-    <t>Easy option A30</t>
-  </si>
-  <si>
-    <t>Hard option B1</t>
-  </si>
-  <si>
-    <t>Hard option B2</t>
-  </si>
-  <si>
-    <t>Hard option B3</t>
-  </si>
-  <si>
-    <t>Hard option B4</t>
-  </si>
-  <si>
-    <t>Hard option B5</t>
-  </si>
-  <si>
-    <t>Hard option B6</t>
-  </si>
-  <si>
-    <t>Hard option B7</t>
-  </si>
-  <si>
-    <t>Hard option B8</t>
-  </si>
-  <si>
-    <t>Hard option B9</t>
-  </si>
-  <si>
-    <t>Hard option B10</t>
-  </si>
-  <si>
-    <t>Hard option B11</t>
-  </si>
-  <si>
-    <t>Hard option B12</t>
-  </si>
-  <si>
-    <t>Medium option B1</t>
-  </si>
-  <si>
-    <t>Medium option B2</t>
-  </si>
-  <si>
-    <t>Medium option B3</t>
-  </si>
-  <si>
-    <t>Medium option B4</t>
-  </si>
-  <si>
-    <t>Medium option B5</t>
-  </si>
-  <si>
-    <t>Medium option B6</t>
-  </si>
-  <si>
-    <t>Medium option B7</t>
-  </si>
-  <si>
-    <t>Medium option B8</t>
-  </si>
-  <si>
-    <t>Medium option B9</t>
-  </si>
-  <si>
-    <t>Medium option B10</t>
-  </si>
-  <si>
-    <t>Medium option B11</t>
-  </si>
-  <si>
-    <t>Medium option B12</t>
-  </si>
-  <si>
-    <t>Medium option B13</t>
-  </si>
-  <si>
-    <t>Medium option B14</t>
-  </si>
-  <si>
-    <t>Medium option B15</t>
-  </si>
-  <si>
-    <t>Medium option B16</t>
-  </si>
-  <si>
-    <t>Medium option B17</t>
-  </si>
-  <si>
-    <t>Medium option B18</t>
-  </si>
-  <si>
-    <t>Medium option B19</t>
-  </si>
-  <si>
-    <t>Medium option B20</t>
-  </si>
-  <si>
-    <t>Medium option B21</t>
-  </si>
-  <si>
-    <t>Medium option B22</t>
-  </si>
-  <si>
-    <t>Medium option B23</t>
-  </si>
-  <si>
-    <t>Medium option B24</t>
-  </si>
-  <si>
-    <t>Medium option B25</t>
-  </si>
-  <si>
-    <t>Medium option B26</t>
-  </si>
-  <si>
-    <t>Medium option B27</t>
-  </si>
-  <si>
-    <t>Medium option B28</t>
-  </si>
-  <si>
-    <t>Medium option B29</t>
-  </si>
-  <si>
-    <t>Medium option B30</t>
-  </si>
-  <si>
-    <t>Easy option B1</t>
-  </si>
-  <si>
-    <t>Easy option B2</t>
-  </si>
-  <si>
-    <t>Easy option B3</t>
-  </si>
-  <si>
-    <t>Easy option B4</t>
-  </si>
-  <si>
-    <t>Easy option B5</t>
-  </si>
-  <si>
-    <t>Easy option B6</t>
-  </si>
-  <si>
-    <t>Easy option B7</t>
-  </si>
-  <si>
-    <t>Easy option B8</t>
-  </si>
-  <si>
-    <t>Easy option B9</t>
-  </si>
-  <si>
-    <t>Easy option B10</t>
-  </si>
-  <si>
-    <t>Easy option B11</t>
-  </si>
-  <si>
-    <t>Easy option B12</t>
-  </si>
-  <si>
-    <t>Easy option B13</t>
-  </si>
-  <si>
-    <t>Easy option B14</t>
-  </si>
-  <si>
-    <t>Easy option B15</t>
-  </si>
-  <si>
-    <t>Easy option B16</t>
-  </si>
-  <si>
-    <t>Easy option B17</t>
-  </si>
-  <si>
-    <t>Easy option B18</t>
-  </si>
-  <si>
-    <t>Easy option B19</t>
-  </si>
-  <si>
-    <t>Easy option B20</t>
-  </si>
-  <si>
-    <t>Easy option B21</t>
-  </si>
-  <si>
-    <t>Easy option B22</t>
-  </si>
-  <si>
-    <t>Easy option B23</t>
-  </si>
-  <si>
-    <t>Easy option B24</t>
-  </si>
-  <si>
-    <t>Easy option B25</t>
-  </si>
-  <si>
-    <t>Easy option B26</t>
-  </si>
-  <si>
-    <t>Easy option B27</t>
-  </si>
-  <si>
-    <t>Easy option B28</t>
-  </si>
-  <si>
-    <t>Easy option B29</t>
-  </si>
-  <si>
-    <t>Easy option B30</t>
-  </si>
-  <si>
-    <t>Hard option C1</t>
-  </si>
-  <si>
-    <t>Hard option C2</t>
-  </si>
-  <si>
-    <t>Hard option C3</t>
-  </si>
-  <si>
-    <t>Hard option C4</t>
-  </si>
-  <si>
-    <t>Hard option C5</t>
-  </si>
-  <si>
-    <t>Hard option C6</t>
-  </si>
-  <si>
-    <t>Hard option C7</t>
-  </si>
-  <si>
-    <t>Hard option C8</t>
-  </si>
-  <si>
-    <t>Hard option C9</t>
-  </si>
-  <si>
-    <t>Hard option C10</t>
-  </si>
-  <si>
-    <t>Hard option C11</t>
-  </si>
-  <si>
-    <t>Hard option C12</t>
-  </si>
-  <si>
-    <t>Medium option C1</t>
-  </si>
-  <si>
-    <t>Medium option C2</t>
-  </si>
-  <si>
-    <t>Medium option C3</t>
-  </si>
-  <si>
-    <t>Medium option C4</t>
-  </si>
-  <si>
-    <t>Medium option C5</t>
-  </si>
-  <si>
-    <t>Medium option C6</t>
-  </si>
-  <si>
-    <t>Medium option C7</t>
-  </si>
-  <si>
-    <t>Medium option C8</t>
-  </si>
-  <si>
-    <t>Medium option C9</t>
-  </si>
-  <si>
-    <t>Medium option C10</t>
-  </si>
-  <si>
-    <t>Medium option C11</t>
-  </si>
-  <si>
-    <t>Medium option C12</t>
-  </si>
-  <si>
-    <t>Medium option C13</t>
-  </si>
-  <si>
-    <t>Medium option C14</t>
-  </si>
-  <si>
-    <t>Medium option C15</t>
-  </si>
-  <si>
-    <t>Medium option C16</t>
-  </si>
-  <si>
-    <t>Medium option C17</t>
-  </si>
-  <si>
-    <t>Medium option C18</t>
-  </si>
-  <si>
-    <t>Medium option C19</t>
-  </si>
-  <si>
-    <t>Medium option C20</t>
-  </si>
-  <si>
-    <t>Medium option C21</t>
-  </si>
-  <si>
-    <t>Medium option C22</t>
-  </si>
-  <si>
-    <t>Medium option C23</t>
-  </si>
-  <si>
-    <t>Medium option C24</t>
-  </si>
-  <si>
-    <t>Medium option C25</t>
-  </si>
-  <si>
-    <t>Medium option C26</t>
-  </si>
-  <si>
-    <t>Medium option C27</t>
-  </si>
-  <si>
-    <t>Medium option C28</t>
-  </si>
-  <si>
-    <t>Medium option C29</t>
-  </si>
-  <si>
-    <t>Medium option C30</t>
-  </si>
-  <si>
-    <t>Easy option C1</t>
-  </si>
-  <si>
-    <t>Easy option C2</t>
-  </si>
-  <si>
-    <t>Easy option C3</t>
-  </si>
-  <si>
-    <t>Easy option C4</t>
-  </si>
-  <si>
-    <t>Easy option C5</t>
-  </si>
-  <si>
-    <t>Easy option C6</t>
-  </si>
-  <si>
-    <t>Easy option C7</t>
-  </si>
-  <si>
-    <t>Easy option C8</t>
-  </si>
-  <si>
-    <t>Easy option C9</t>
-  </si>
-  <si>
-    <t>Easy option C10</t>
-  </si>
-  <si>
-    <t>Easy option C11</t>
-  </si>
-  <si>
-    <t>Easy option C12</t>
-  </si>
-  <si>
-    <t>Easy option C13</t>
-  </si>
-  <si>
-    <t>Easy option C14</t>
-  </si>
-  <si>
-    <t>Easy option C15</t>
-  </si>
-  <si>
-    <t>Easy option C16</t>
-  </si>
-  <si>
-    <t>Easy option C17</t>
-  </si>
-  <si>
-    <t>Easy option C18</t>
-  </si>
-  <si>
-    <t>Easy option C19</t>
-  </si>
-  <si>
-    <t>Easy option C20</t>
-  </si>
-  <si>
-    <t>Easy option C21</t>
-  </si>
-  <si>
-    <t>Easy option C22</t>
-  </si>
-  <si>
-    <t>Easy option C23</t>
-  </si>
-  <si>
-    <t>Easy option C24</t>
-  </si>
-  <si>
-    <t>Easy option C25</t>
-  </si>
-  <si>
-    <t>Easy option C26</t>
-  </si>
-  <si>
-    <t>Easy option C27</t>
-  </si>
-  <si>
-    <t>Easy option C28</t>
-  </si>
-  <si>
-    <t>Easy option C29</t>
-  </si>
-  <si>
-    <t>Easy option C30</t>
-  </si>
-  <si>
-    <t>Hard option D1</t>
-  </si>
-  <si>
-    <t>Hard option D2</t>
-  </si>
-  <si>
-    <t>Hard option D3</t>
-  </si>
-  <si>
-    <t>Hard option D4</t>
-  </si>
-  <si>
-    <t>Hard option D5</t>
-  </si>
-  <si>
-    <t>Hard option D6</t>
-  </si>
-  <si>
-    <t>Hard option D7</t>
-  </si>
-  <si>
-    <t>Hard option D8</t>
-  </si>
-  <si>
-    <t>Hard option D9</t>
-  </si>
-  <si>
-    <t>Hard option D10</t>
-  </si>
-  <si>
-    <t>Hard option D11</t>
-  </si>
-  <si>
-    <t>Hard option D12</t>
-  </si>
-  <si>
-    <t>Medium option D1</t>
-  </si>
-  <si>
-    <t>Medium option D2</t>
-  </si>
-  <si>
-    <t>Medium option D3</t>
-  </si>
-  <si>
-    <t>Medium option D4</t>
-  </si>
-  <si>
-    <t>Medium option D5</t>
-  </si>
-  <si>
-    <t>Medium option D6</t>
-  </si>
-  <si>
-    <t>Medium option D7</t>
-  </si>
-  <si>
-    <t>Medium option D8</t>
-  </si>
-  <si>
-    <t>Medium option D9</t>
-  </si>
-  <si>
-    <t>Medium option D10</t>
-  </si>
-  <si>
-    <t>Medium option D11</t>
-  </si>
-  <si>
-    <t>Medium option D12</t>
-  </si>
-  <si>
-    <t>Medium option D13</t>
-  </si>
-  <si>
-    <t>Medium option D14</t>
-  </si>
-  <si>
-    <t>Medium option D15</t>
-  </si>
-  <si>
-    <t>Medium option D16</t>
-  </si>
-  <si>
-    <t>Medium option D17</t>
-  </si>
-  <si>
-    <t>Medium option D18</t>
-  </si>
-  <si>
-    <t>Medium option D19</t>
-  </si>
-  <si>
-    <t>Medium option D20</t>
-  </si>
-  <si>
-    <t>Medium option D21</t>
-  </si>
-  <si>
-    <t>Medium option D22</t>
-  </si>
-  <si>
-    <t>Medium option D23</t>
-  </si>
-  <si>
-    <t>Medium option D24</t>
-  </si>
-  <si>
-    <t>Medium option D25</t>
-  </si>
-  <si>
-    <t>Medium option D26</t>
-  </si>
-  <si>
-    <t>Medium option D27</t>
-  </si>
-  <si>
-    <t>Medium option D28</t>
-  </si>
-  <si>
-    <t>Medium option D29</t>
-  </si>
-  <si>
-    <t>Medium option D30</t>
-  </si>
-  <si>
-    <t>Easy option D1</t>
-  </si>
-  <si>
-    <t>Easy option D2</t>
-  </si>
-  <si>
-    <t>Easy option D3</t>
-  </si>
-  <si>
-    <t>Easy option D4</t>
-  </si>
-  <si>
-    <t>Easy option D5</t>
-  </si>
-  <si>
-    <t>Easy option D6</t>
-  </si>
-  <si>
-    <t>Easy option D7</t>
-  </si>
-  <si>
-    <t>Easy option D8</t>
-  </si>
-  <si>
-    <t>Easy option D9</t>
-  </si>
-  <si>
-    <t>Easy option D10</t>
-  </si>
-  <si>
-    <t>Easy option D11</t>
-  </si>
-  <si>
-    <t>Easy option D12</t>
-  </si>
-  <si>
-    <t>Easy option D13</t>
-  </si>
-  <si>
-    <t>Easy option D14</t>
-  </si>
-  <si>
-    <t>Easy option D15</t>
-  </si>
-  <si>
-    <t>Easy option D16</t>
-  </si>
-  <si>
-    <t>Easy option D17</t>
-  </si>
-  <si>
-    <t>Easy option D18</t>
-  </si>
-  <si>
-    <t>Easy option D19</t>
-  </si>
-  <si>
-    <t>Easy option D20</t>
-  </si>
-  <si>
-    <t>Easy option D21</t>
-  </si>
-  <si>
-    <t>Easy option D22</t>
-  </si>
-  <si>
-    <t>Easy option D23</t>
-  </si>
-  <si>
-    <t>Easy option D24</t>
-  </si>
-  <si>
-    <t>Easy option D25</t>
-  </si>
-  <si>
-    <t>Easy option D26</t>
-  </si>
-  <si>
-    <t>Easy option D27</t>
-  </si>
-  <si>
-    <t>Easy option D28</t>
-  </si>
-  <si>
-    <t>Easy option D29</t>
-  </si>
-  <si>
-    <t>Easy option D30</t>
+    <t>What is the primary purpose of a SWOT analysis?</t>
+  </si>
+  <si>
+    <t>What does a company's mission statement describe?</t>
+  </si>
+  <si>
+    <t>In a competitive market, what is a barrier to entry?</t>
+  </si>
+  <si>
+    <t>What is meant by economies of scale?</t>
+  </si>
+  <si>
+    <t>What does market segmentation involve?</t>
+  </si>
+  <si>
+    <t>What is a company's value proposition?</t>
+  </si>
+  <si>
+    <t>What is the main function of working capital?</t>
+  </si>
+  <si>
+    <t>What does a break-even point represent?</t>
+  </si>
+  <si>
+    <t>Why do firms diversify into new markets?</t>
+  </si>
+  <si>
+    <t>What is a core competency?</t>
+  </si>
+  <si>
+    <t>What is the role of a board of directors?</t>
+  </si>
+  <si>
+    <t>What does 'first-mover advantage' refer to?</t>
+  </si>
+  <si>
+    <t>What is the purpose of a cash flow forecast?</t>
+  </si>
+  <si>
+    <t>What is brand equity?</t>
+  </si>
+  <si>
+    <t>What does outsourcing typically allow a firm to do?</t>
+  </si>
+  <si>
+    <t>What is a supply chain?</t>
+  </si>
+  <si>
+    <t>What is the aim of benchmarking?</t>
+  </si>
+  <si>
+    <t>What does a merger involve?</t>
+  </si>
+  <si>
+    <t>What is meant by a firm's operating margin?</t>
+  </si>
+  <si>
+    <t>Why is customer retention valuable?</t>
+  </si>
+  <si>
+    <t>What is a stakeholder?</t>
+  </si>
+  <si>
+    <t>What does 'due diligence' mean ahead of an acquisition?</t>
+  </si>
+  <si>
+    <t>What is the purpose of a pilot launch?</t>
+  </si>
+  <si>
+    <t>What is a fixed cost?</t>
+  </si>
+  <si>
+    <t>What does a distribution channel do?</t>
+  </si>
+  <si>
+    <t>Why might a firm license its technology to others?</t>
+  </si>
+  <si>
+    <t>What is the importance of aligning internal capabilities with external opportunities?</t>
+  </si>
+  <si>
+    <t>What does a profit and loss statement show?</t>
+  </si>
+  <si>
+    <t>What is the purpose of market research?</t>
+  </si>
+  <si>
+    <t>What is a competitive advantage?</t>
+  </si>
+  <si>
+    <t>What does inventory turnover measure?</t>
+  </si>
+  <si>
+    <t>Why do organisations use KPIs?</t>
+  </si>
+  <si>
+    <t>What is a joint venture?</t>
+  </si>
+  <si>
+    <t>What is the purpose of a business model?</t>
+  </si>
+  <si>
+    <t>What does 'time to market' measure?</t>
+  </si>
+  <si>
+    <t>Why is cash different from profit?</t>
+  </si>
+  <si>
+    <t>What is a niche market?</t>
+  </si>
+  <si>
+    <t>What does organisational culture refer to?</t>
+  </si>
+  <si>
+    <t>What is the purpose of a budget?</t>
+  </si>
+  <si>
+    <t>What is meant by 'scalability'?</t>
+  </si>
+  <si>
+    <t>Why do firms conduct competitor analysis?</t>
+  </si>
+  <si>
+    <t>What is the role of a supplier contract?</t>
+  </si>
+  <si>
+    <t>What does customer lifetime value estimate?</t>
+  </si>
+  <si>
+    <t>What is a strategic objective?</t>
+  </si>
+  <si>
+    <t>What does 'return on investment' compare?</t>
+  </si>
+  <si>
+    <t>Why is delegation important for a manager?</t>
+  </si>
+  <si>
+    <t>What is a product life cycle?</t>
+  </si>
+  <si>
+    <t>What does 'differentiation' mean as a strategy?</t>
+  </si>
+  <si>
+    <t>What is the purpose of an organisational structure?</t>
+  </si>
+  <si>
+    <t>Why do businesses hold buffer stock?</t>
+  </si>
+  <si>
+    <t>What is meant by 'market share'?</t>
+  </si>
+  <si>
+    <t>What does a feasibility study assess?</t>
+  </si>
+  <si>
+    <t>Why is a diverse team often an advantage?</t>
+  </si>
+  <si>
+    <t>What is 'churn rate'?</t>
+  </si>
+  <si>
+    <t>What is the purpose of quality control?</t>
+  </si>
+  <si>
+    <t>What does 'liquidity' describe?</t>
+  </si>
+  <si>
+    <t>Why might a firm choose a franchise model?</t>
+  </si>
+  <si>
+    <t>What is a target audience?</t>
+  </si>
+  <si>
+    <t>What does 'lead time' mean?</t>
+  </si>
+  <si>
+    <t>Why do companies publish annual reports?</t>
+  </si>
+  <si>
+    <t>What is 'opportunity cost'?</t>
+  </si>
+  <si>
+    <t>What does a Gantt chart display?</t>
+  </si>
+  <si>
+    <t>What is meant by 'vertical integration'?</t>
+  </si>
+  <si>
+    <t>Why is a contingency plan useful?</t>
+  </si>
+  <si>
+    <t>What does 'gross profit' equal?</t>
+  </si>
+  <si>
+    <t>What is the purpose of a service level agreement?</t>
+  </si>
+  <si>
+    <t>Why do firms invest in staff training?</t>
+  </si>
+  <si>
+    <t>What is 'price elasticity of demand'?</t>
+  </si>
+  <si>
+    <t>What does a risk register record?</t>
+  </si>
+  <si>
+    <t>Why is market positioning important?</t>
+  </si>
+  <si>
+    <t>What is 'capacity utilisation'?</t>
+  </si>
+  <si>
+    <t>What does a customer feedback loop enable?</t>
+  </si>
+  <si>
+    <t>To calculate a company's quarterly tax liability</t>
+  </si>
+  <si>
+    <t>The exact revenue target for the next quarter</t>
+  </si>
+  <si>
+    <t>A tariff paid by existing firms on exports</t>
+  </si>
+  <si>
+    <t>Cost per unit falls as output volume rises</t>
+  </si>
+  <si>
+    <t>Reducing the number of products a firm sells</t>
+  </si>
+  <si>
+    <t>The total book value of its fixed assets</t>
+  </si>
+  <si>
+    <t>To pay long-term shareholder dividends</t>
+  </si>
+  <si>
+    <t>The sales level at which total revenue equals total cost</t>
+  </si>
+  <si>
+    <t>To guarantee a higher share price within a year</t>
+  </si>
+  <si>
+    <t>The department with the largest headcount</t>
+  </si>
+  <si>
+    <t>To handle day-to-day customer complaints</t>
+  </si>
+  <si>
+    <t>The benefit a firm gains by entering a market before its rivals</t>
+  </si>
+  <si>
+    <t>To record historic profits for tax purposes</t>
+  </si>
+  <si>
+    <t>The share of a company owned by its founders</t>
+  </si>
+  <si>
+    <t>Increase the number of shares in issue</t>
+  </si>
+  <si>
+    <t>The network of organisations involved in producing and delivering a product</t>
+  </si>
+  <si>
+    <t>To set the opening price of a new share issue</t>
+  </si>
+  <si>
+    <t>One company lending money to another</t>
+  </si>
+  <si>
+    <t>The gap between the highest and lowest salary</t>
+  </si>
+  <si>
+    <t>Keeping an existing customer usually costs less than winning a new one</t>
+  </si>
+  <si>
+    <t>Only a person who owns shares in the company</t>
+  </si>
+  <si>
+    <t>Announcing the deal to the press in advance</t>
+  </si>
+  <si>
+    <t>To train pilots to operate company aircraft</t>
+  </si>
+  <si>
+    <t>A cost that does not change with the level of output in the short run</t>
+  </si>
+  <si>
+    <t>Sets the manufacturing schedule for a factory</t>
+  </si>
+  <si>
+    <t>To surrender ownership of its patents permanently</t>
+  </si>
+  <si>
+    <t>It is more relevant for small-mid sized startups</t>
+  </si>
+  <si>
+    <t>Revenues and expenses across a defined period</t>
+  </si>
+  <si>
+    <t>To increase the price of an existing product</t>
+  </si>
+  <si>
+    <t>Any product that is cheaper than the average</t>
+  </si>
+  <si>
+    <t>The number of warehouses a firm operates</t>
+  </si>
+  <si>
+    <t>To track progress against objectives using agreed measures</t>
+  </si>
+  <si>
+    <t>A loan made jointly by two banks</t>
+  </si>
+  <si>
+    <t>To list the furniture and equipment owned</t>
+  </si>
+  <si>
+    <t>The opening hours of a retail outlet</t>
+  </si>
+  <si>
+    <t>A firm can record a profit and still lack the cash to pay its bills</t>
+  </si>
+  <si>
+    <t>A market in which prices never change</t>
+  </si>
+  <si>
+    <t>The physical design of the office building</t>
+  </si>
+  <si>
+    <t>To calculate the market value of shares</t>
+  </si>
+  <si>
+    <t>The ability to grow output or users without a proportional rise in cost</t>
+  </si>
+  <si>
+    <t>To agree prices jointly with rivals</t>
+  </si>
+  <si>
+    <t>To transfer ownership of the supplier to the buyer</t>
+  </si>
+  <si>
+    <t>The age of the average customer</t>
+  </si>
+  <si>
+    <t>A daily task assigned to a team member</t>
+  </si>
+  <si>
+    <t>The number of investors against the share price</t>
+  </si>
+  <si>
+    <t>It frees the manager's time and develops the capability of the team</t>
+  </si>
+  <si>
+    <t>The warranty period offered to buyers</t>
+  </si>
+  <si>
+    <t>Charging the lowest price in the market</t>
+  </si>
+  <si>
+    <t>To set the company's annual revenue target</t>
+  </si>
+  <si>
+    <t>To absorb unexpected swings in demand or supply</t>
+  </si>
+  <si>
+    <t>The percentage of a company owned by its founder</t>
+  </si>
+  <si>
+    <t>How satisfied current employees are</t>
+  </si>
+  <si>
+    <t>It reduces the need for team meetings</t>
+  </si>
+  <si>
+    <t>The proportion of customers who stop buying over a given period</t>
+  </si>
+  <si>
+    <t>To increase production speed regardless of defects</t>
+  </si>
+  <si>
+    <t>The volume of goods a firm can store</t>
+  </si>
+  <si>
+    <t>To avoid having to set any brand standards</t>
+  </si>
+  <si>
+    <t>The specific group a product or message is intended to reach</t>
+  </si>
+  <si>
+    <t>The time a manager spends leading meetings</t>
+  </si>
+  <si>
+    <t>To advertise products to new customers</t>
+  </si>
+  <si>
+    <t>The fee charged to enter a new market</t>
+  </si>
+  <si>
+    <t>Project tasks and their durations across a timeline</t>
+  </si>
+  <si>
+    <t>Promoting staff into more senior positions</t>
+  </si>
+  <si>
+    <t>It removes all risk from a project</t>
+  </si>
+  <si>
+    <t>Revenue less every expense including tax</t>
+  </si>
+  <si>
+    <t>To define the standard of service a provider commits to deliver</t>
+  </si>
+  <si>
+    <t>To reduce the number of roles required</t>
+  </si>
+  <si>
+    <t>The range of prices a retailer may legally charge</t>
+  </si>
+  <si>
+    <t>The names of everyone who has taken a loan</t>
+  </si>
+  <si>
+    <t>It shapes how customers perceive an offering relative to alternatives</t>
+  </si>
+  <si>
+    <t>The share of office desks currently occupied</t>
+  </si>
+  <si>
+    <t>Customers to be billed automatically each month</t>
+  </si>
+  <si>
+    <t>To assess internal strengths and weaknesses alongside external opportunities and threats</t>
+  </si>
+  <si>
+    <t>The legal structure of the shareholding</t>
+  </si>
+  <si>
+    <t>A clause preventing employees from taking leave</t>
+  </si>
+  <si>
+    <t>Prices rise automatically in line with inflation</t>
+  </si>
+  <si>
+    <t>Dividing a broad market into groups of buyers with similar needs</t>
+  </si>
+  <si>
+    <t>The dividend paid per share each year</t>
+  </si>
+  <si>
+    <t>To purchase manufacturing plants outright</t>
+  </si>
+  <si>
+    <t>The point at which a product is withdrawn from sale</t>
+  </si>
+  <si>
+    <t>To reduce dependence on a single source of revenue</t>
+  </si>
+  <si>
+    <t>The oldest product still in the catalogue</t>
+  </si>
+  <si>
+    <t>To approve individual purchase orders</t>
+  </si>
+  <si>
+    <t>The discount offered to the first customer of the day</t>
+  </si>
+  <si>
+    <t>To anticipate when money will enter and leave the business</t>
+  </si>
+  <si>
+    <t>The cost of registering a trademark</t>
+  </si>
+  <si>
+    <t>Avoid paying value-added tax</t>
+  </si>
+  <si>
+    <t>A queue of customers waiting for a service</t>
+  </si>
+  <si>
+    <t>To compare performance against a strong reference point and identify gaps</t>
+  </si>
+  <si>
+    <t>A firm splitting its shares into smaller units</t>
+  </si>
+  <si>
+    <t>The interest rate charged on its overdraft</t>
+  </si>
+  <si>
+    <t>Existing customers are exempt from price increases</t>
+  </si>
+  <si>
+    <t>Any party affected by, or able to affect, the organisation's activities</t>
+  </si>
+  <si>
+    <t>Paying a deposit into the seller's bank account</t>
+  </si>
+  <si>
+    <t>To reduce the product's manufacturing cost</t>
+  </si>
+  <si>
+    <t>A cost that is paid on a fixed date each month</t>
+  </si>
+  <si>
+    <t>Carries a product from producer through to the end customer</t>
+  </si>
+  <si>
+    <t>To avoid publishing its annual accounts</t>
+  </si>
+  <si>
+    <t>It guarantees market share dominance</t>
+  </si>
+  <si>
+    <t>The company's assets at a single moment in time</t>
+  </si>
+  <si>
+    <t>To gather evidence about customer needs and market conditions before deciding</t>
+  </si>
+  <si>
+    <t>The largest advertising budget in the sector</t>
+  </si>
+  <si>
+    <t>The value of stock lost to damage</t>
+  </si>
+  <si>
+    <t>To replace the need for financial accounts</t>
+  </si>
+  <si>
+    <t>A shared enterprise in which two firms pool resources for a specific purpose</t>
+  </si>
+  <si>
+    <t>To record the minutes of board meetings</t>
+  </si>
+  <si>
+    <t>The delay between an order and its payment</t>
+  </si>
+  <si>
+    <t>Profit is always larger than the cash held</t>
+  </si>
+  <si>
+    <t>A narrow, specialised segment with distinct needs</t>
+  </si>
+  <si>
+    <t>The list of public holidays observed</t>
+  </si>
+  <si>
+    <t>To record customer complaints</t>
+  </si>
+  <si>
+    <t>The ability to weigh goods accurately</t>
+  </si>
+  <si>
+    <t>To understand rivals' positions and anticipate their moves</t>
+  </si>
+  <si>
+    <t>To guarantee the supplier's profitability</t>
+  </si>
+  <si>
+    <t>The total profit expected from a customer across the whole relationship</t>
+  </si>
+  <si>
+    <t>A rule about workplace dress code</t>
+  </si>
+  <si>
+    <t>The salary of managers against that of staff</t>
+  </si>
+  <si>
+    <t>It removes the manager's accountability entirely</t>
+  </si>
+  <si>
+    <t>The stages a product passes through from introduction to decline</t>
+  </si>
+  <si>
+    <t>Selling in as many countries as possible</t>
+  </si>
+  <si>
+    <t>To determine the dividend policy</t>
+  </si>
+  <si>
+    <t>To increase the value of the company's shares</t>
+  </si>
+  <si>
+    <t>A firm's sales expressed as a proportion of total market sales</t>
+  </si>
+  <si>
+    <t>The historic accuracy of past accounts</t>
+  </si>
+  <si>
+    <t>It removes the requirement for a manager</t>
+  </si>
+  <si>
+    <t>The speed at which stock moves through a warehouse</t>
+  </si>
+  <si>
+    <t>To ensure output consistently meets defined standards</t>
+  </si>
+  <si>
+    <t>The total value of a company's debt</t>
+  </si>
+  <si>
+    <t>To transfer its tax obligations to others</t>
+  </si>
+  <si>
+    <t>Everyone who has ever visited the website</t>
+  </si>
+  <si>
+    <t>The time between placing an order and receiving it</t>
+  </si>
+  <si>
+    <t>To recruit candidates for vacancies</t>
+  </si>
+  <si>
+    <t>The cost of missed delivery deadlines</t>
+  </si>
+  <si>
+    <t>A company's profits by product line</t>
+  </si>
+  <si>
+    <t>Taking ownership of stages further up or down one's own supply chain</t>
+  </si>
+  <si>
+    <t>It replaces the need for insurance</t>
+  </si>
+  <si>
+    <t>The cash held at the end of the year</t>
+  </si>
+  <si>
+    <t>To set the wages of the provider's staff</t>
+  </si>
+  <si>
+    <t>To build the skills the organisation needs to perform and adapt</t>
+  </si>
+  <si>
+    <t>The speed at which prices are updated</t>
+  </si>
+  <si>
+    <t>Accidents that occurred on site last year</t>
+  </si>
+  <si>
+    <t>It determines where a shop is physically built</t>
+  </si>
+  <si>
+    <t>The proportion of potential output that is actually being produced</t>
+  </si>
+  <si>
+    <t>Refunds to be processed without any approval</t>
+  </si>
+  <si>
+    <t>To schedule production runs across factories</t>
+  </si>
+  <si>
+    <t>The organisation's core purpose and reason for existing</t>
+  </si>
+  <si>
+    <t>A limit on how many products a firm may advertise</t>
+  </si>
+  <si>
+    <t>Staff numbers grow in step with revenue</t>
+  </si>
+  <si>
+    <t>Merging two competing companies</t>
+  </si>
+  <si>
+    <t>The specific benefit it promises to deliver to a chosen customer</t>
+  </si>
+  <si>
+    <t>To settle corporate income tax arrears</t>
+  </si>
+  <si>
+    <t>The maximum output a factory can physically produce</t>
+  </si>
+  <si>
+    <t>To avoid having to file annual accounts</t>
+  </si>
+  <si>
+    <t>A capability a firm performs distinctively well and that rivals struggle to imitate</t>
+  </si>
+  <si>
+    <t>To deliver staff training sessions</t>
+  </si>
+  <si>
+    <t>The right to speak first at a shareholder meeting</t>
+  </si>
+  <si>
+    <t>To place a valuation on the company's brand</t>
+  </si>
+  <si>
+    <t>The commercial value that arises from customer perception of a brand</t>
+  </si>
+  <si>
+    <t>Extend its patent protection period</t>
+  </si>
+  <si>
+    <t>A sequence of managers in a reporting line</t>
+  </si>
+  <si>
+    <t>To calculate depreciation on equipment</t>
+  </si>
+  <si>
+    <t>Two companies combining to form a single entity</t>
+  </si>
+  <si>
+    <t>The proportion of staff working overtime</t>
+  </si>
+  <si>
+    <t>Retained customers reduce a firm's tax bill</t>
+  </si>
+  <si>
+    <t>An employee who has served more than ten years</t>
+  </si>
+  <si>
+    <t>Investigating the target's finances, risks and obligations before committing</t>
+  </si>
+  <si>
+    <t>To register the product's design rights</t>
+  </si>
+  <si>
+    <t>A price agreed with a customer in advance</t>
+  </si>
+  <si>
+    <t>Determines the interest charged on trade credit</t>
+  </si>
+  <si>
+    <t>To earn revenue from the technology without manufacturing it itself</t>
+  </si>
+  <si>
+    <t>It reduces the need for innovation and cost reduction</t>
+  </si>
+  <si>
+    <t>The names of all current shareholders</t>
+  </si>
+  <si>
+    <t>To recruit staff for the sales department</t>
+  </si>
+  <si>
+    <t>Something that lets a firm outperform rivals in a way they struggle to copy</t>
+  </si>
+  <si>
+    <t>The cost of transporting goods to stores</t>
+  </si>
+  <si>
+    <t>To set the salary of every employee</t>
+  </si>
+  <si>
+    <t>A product sold under two different names</t>
+  </si>
+  <si>
+    <t>To explain how the organisation creates, delivers and captures value</t>
+  </si>
+  <si>
+    <t>The duration of an advertising campaign</t>
+  </si>
+  <si>
+    <t>Cash is taxed but profit is not</t>
+  </si>
+  <si>
+    <t>The largest segment in an industry</t>
+  </si>
+  <si>
+    <t>The shared values and norms that shape how people behave at work</t>
+  </si>
+  <si>
+    <t>To define the company's brand colours</t>
+  </si>
+  <si>
+    <t>A fixed legal limit on company size</t>
+  </si>
+  <si>
+    <t>To share customer lists across the industry</t>
+  </si>
+  <si>
+    <t>To set out agreed terms of supply, price and obligations</t>
+  </si>
+  <si>
+    <t>The number of products in the catalogue</t>
+  </si>
+  <si>
+    <t>A specific, longer-term goal that supports the organisation's direction</t>
+  </si>
+  <si>
+    <t>The tax paid against the revenue earned</t>
+  </si>
+  <si>
+    <t>It reduces the number of staff required</t>
+  </si>
+  <si>
+    <t>The time taken to assemble a single unit</t>
+  </si>
+  <si>
+    <t>Offering something customers value that rivals do not match</t>
+  </si>
+  <si>
+    <t>To choose the firm's suppliers</t>
+  </si>
+  <si>
+    <t>To reduce the cost of each unit produced</t>
+  </si>
+  <si>
+    <t>The number of retail outlets it operates</t>
+  </si>
+  <si>
+    <t>Whether a proposed project is practical and worth pursuing</t>
+  </si>
+  <si>
+    <t>It guarantees unanimous decisions</t>
+  </si>
+  <si>
+    <t>The rate at which prices rise</t>
+  </si>
+  <si>
+    <t>To set the selling price of goods</t>
+  </si>
+  <si>
+    <t>How easily assets can be converted into cash</t>
+  </si>
+  <si>
+    <t>To stop competitors from advertising</t>
+  </si>
+  <si>
+    <t>The audience present at a shareholder meeting</t>
+  </si>
+  <si>
+    <t>The period remaining before a patent expires</t>
+  </si>
+  <si>
+    <t>To give shareholders and others an account of performance and position</t>
+  </si>
+  <si>
+    <t>The penalty for cancelling a contract</t>
+  </si>
+  <si>
+    <t>The distribution of salaries within a team</t>
+  </si>
+  <si>
+    <t>Stacking inventory more efficiently in a warehouse</t>
+  </si>
+  <si>
+    <t>It prepares a response in advance for things that may go wrong</t>
+  </si>
+  <si>
+    <t>The total value of unsold stock</t>
+  </si>
+  <si>
+    <t>To transfer ownership of the service</t>
+  </si>
+  <si>
+    <t>To satisfy an annual advertising quota</t>
+  </si>
+  <si>
+    <t>How much demand responds to a change in price</t>
+  </si>
+  <si>
+    <t>The insurance premiums paid annually</t>
+  </si>
+  <si>
+    <t>It fixes the company's production capacity</t>
+  </si>
+  <si>
+    <t>The percentage of invoices paid on time</t>
+  </si>
+  <si>
+    <t>Insight from users to flow back and shape future improvements</t>
+  </si>
+  <si>
+    <t>To rank employees for annual appraisal</t>
+  </si>
+  <si>
+    <t>The seating layout of the head office</t>
+  </si>
+  <si>
+    <t>A condition that makes it difficult for new firms to start competing in an industry</t>
+  </si>
+  <si>
+    <t>Every department receives an equal budget</t>
+  </si>
+  <si>
+    <t>Setting one price for every customer</t>
+  </si>
+  <si>
+    <t>The number of patents it holds</t>
+  </si>
+  <si>
+    <t>To fund day-to-day operating needs such as stock and receivables</t>
+  </si>
+  <si>
+    <t>The date on which a loan must be repaid in full</t>
+  </si>
+  <si>
+    <t>To eliminate the need for market research</t>
+  </si>
+  <si>
+    <t>The minimum qualification required of new hires</t>
+  </si>
+  <si>
+    <t>To oversee management and represent shareholders' interests</t>
+  </si>
+  <si>
+    <t>The priority given to senior staff in promotions</t>
+  </si>
+  <si>
+    <t>To rank suppliers by reliability</t>
+  </si>
+  <si>
+    <t>The total spend on advertising last year</t>
+  </si>
+  <si>
+    <t>Have an external provider perform activities it once did in-house</t>
+  </si>
+  <si>
+    <t>A list of a company's shareholders</t>
+  </si>
+  <si>
+    <t>To measure the physical size of a premises</t>
+  </si>
+  <si>
+    <t>A business relocating its head office</t>
+  </si>
+  <si>
+    <t>Operating profit expressed as a percentage of revenue</t>
+  </si>
+  <si>
+    <t>Long-standing customers require no service support</t>
+  </si>
+  <si>
+    <t>A supplier who has signed an exclusivity deal</t>
+  </si>
+  <si>
+    <t>Appointing the target's staff to new roles</t>
+  </si>
+  <si>
+    <t>To test a product with a limited audience before committing to full rollout</t>
+  </si>
+  <si>
+    <t>The cost that is always largest in the accounts</t>
+  </si>
+  <si>
+    <t>Allocates advertising budget between regions</t>
+  </si>
+  <si>
+    <t>To reduce its employee headcount automatically</t>
+  </si>
+  <si>
+    <t>It creates strategic fit and strengthens competitive advantage</t>
+  </si>
+  <si>
+    <t>The forecast demand for next year</t>
+  </si>
+  <si>
+    <t>To register a company with the authorities</t>
+  </si>
+  <si>
+    <t>A longer trading history than competitors</t>
+  </si>
+  <si>
+    <t>How quickly stock is sold and replaced over a period</t>
+  </si>
+  <si>
+    <t>To decide the company's legal structure</t>
+  </si>
+  <si>
+    <t>A meeting between two boards of directors</t>
+  </si>
+  <si>
+    <t>To schedule staff holidays for the year</t>
+  </si>
+  <si>
+    <t>How long it takes to move from idea to a product customers can buy</t>
+  </si>
+  <si>
+    <t>Profit is only calculated when a business closes</t>
+  </si>
+  <si>
+    <t>A market restricted to a single country</t>
+  </si>
+  <si>
+    <t>The company's registered trading name</t>
+  </si>
+  <si>
+    <t>To plan and control the allocation of financial resources</t>
+  </si>
+  <si>
+    <t>The process of reducing a product range</t>
+  </si>
+  <si>
+    <t>To merge reporting systems with competitors</t>
+  </si>
+  <si>
+    <t>To fix the retail price charged to consumers</t>
+  </si>
+  <si>
+    <t>The length of the product warranty</t>
+  </si>
+  <si>
+    <t>A one-off discount offered to a client</t>
+  </si>
+  <si>
+    <t>The gain from an investment against its cost</t>
+  </si>
+  <si>
+    <t>It guarantees faster decisions in every case</t>
+  </si>
+  <si>
+    <t>The recycling process that follows disposal</t>
+  </si>
+  <si>
+    <t>Producing the largest possible volume</t>
+  </si>
+  <si>
+    <t>To define roles, reporting lines and how work is coordinated</t>
+  </si>
+  <si>
+    <t>To satisfy a legal reporting requirement</t>
+  </si>
+  <si>
+    <t>The share price relative to earnings</t>
+  </si>
+  <si>
+    <t>The market value of the company's premises</t>
+  </si>
+  <si>
+    <t>A wider range of perspectives tends to improve problem solving</t>
+  </si>
+  <si>
+    <t>The frequency of board meetings</t>
+  </si>
+  <si>
+    <t>To decide which markets to enter</t>
+  </si>
+  <si>
+    <t>The number of transactions processed per day</t>
+  </si>
+  <si>
+    <t>To expand using partners' capital and local knowledge</t>
+  </si>
+  <si>
+    <t>The staff attending a training session</t>
+  </si>
+  <si>
+    <t>The notice period an employee must serve</t>
+  </si>
+  <si>
+    <t>To negotiate prices with suppliers</t>
+  </si>
+  <si>
+    <t>The value of the next best alternative given up when a choice is made</t>
+  </si>
+  <si>
+    <t>The layout of a factory floor</t>
+  </si>
+  <si>
+    <t>Listing shares on a second exchange</t>
+  </si>
+  <si>
+    <t>It guarantees a project will finish early</t>
+  </si>
+  <si>
+    <t>Revenue less the direct cost of goods sold</t>
+  </si>
+  <si>
+    <t>To register a service as a trademark</t>
+  </si>
+  <si>
+    <t>To increase the company's share capital</t>
+  </si>
+  <si>
+    <t>The difference between cost and selling price</t>
+  </si>
+  <si>
+    <t>Identified risks with their likelihood, impact and planned response</t>
+  </si>
+  <si>
+    <t>It sets the legal jurisdiction for disputes</t>
+  </si>
+  <si>
+    <t>The amount of data a server can store</t>
+  </si>
+  <si>
+    <t>Products to be shipped without packaging</t>
   </si>
   <si>
     <t>B</t>
